--- a/docs/HYCU_논문지도시스템_재심사_제출취소_질의서_무하유_2026.10.06.xlsx
+++ b/docs/HYCU_논문지도시스템_재심사_제출취소_질의서_무하유_2026.10.06.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\00_프로젝트\01_한양사이버대\hycu_new\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50464DAE-C484-404D-BB8F-02F3101F7495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18957E85-0F94-47FA-BA6F-F0EA82321761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -239,7 +239,7 @@
     <t>재심 결과를 위원장이 지정한 재심 위원이 확정하는지, 위원장이 다시 최종 판정하는지 확인 부탁드립니다.</t>
   </si>
   <si>
-    <t>위원장이 재심 위원(위원회 전체 또는 특정 위원 1명)과 평가표를 지정</t>
+    <t>위원장이 보완 심사 위원(위원회 전체 또는 특정 위원 1명)과 평가표를 지정 → 다음 번호 심사에서 지정 위원 평가 후 위원장이 최종 판정</t>
   </si>
   <si>
     <t>2-4</t>
@@ -263,7 +263,7 @@
     <t>재심 결과가 불합격인 경우 다음 학기 심사신청부터 재진행하는지 확인 부탁드립니다.</t>
   </si>
   <si>
-    <t>다음 학기 심사신청부터 재진행 (N+1차)</t>
+    <t>다음 학기 심사신청부터 재진행 (다음 번호로 제출)</t>
   </si>
   <si>
     <t>3-1</t>
@@ -309,7 +309,7 @@
     <t>지도교수가 변경된 학생의 새 차수에서 심사위원 구성도 새로 정하는지 확인 부탁드립니다.</t>
   </si>
   <si>
-    <t>지도교수만 변경된 지도교수로 반영</t>
+    <t>목업에는 표현하지 않음 (제안: 지도교수만 변경된 지도교수로 반영, 심사위원은 관리자가 다시 배정)</t>
   </si>
   <si>
     <t>3-4</t>
@@ -594,10 +594,10 @@
     <t>재심 판정 주체</t>
   </si>
   <si>
-    <t>목업: 위원장이 지정한 재심 위원</t>
-  </si>
-  <si>
-    <t>목업: 새로 배정된 심사위원회</t>
+    <t>목업: 위원장이 지정한 보완 심사 위원 평가 후 위원장 최종 판정</t>
+  </si>
+  <si>
+    <t>목업: 관리자가 다시 배정한 심사위원회 (시연 예시는 1차와 같은 구성)</t>
   </si>
   <si>
     <t>질의 2-3, 3-3</t>
